--- a/clients/03de7495/smeta-median-03de7495.xlsx
+++ b/clients/03de7495/smeta-median-03de7495.xlsx
@@ -115,7 +115,7 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Тест · 14 октября 2026 · актуально до 13.11.2026</t>
+          <t xml:space="preserve">Тестовая компания · 14 октября 2026 · актуально до 13.11.2026</t>
         </is>
       </c>
     </row>

--- a/clients/03de7495/smeta-median-03de7495.xlsx
+++ b/clients/03de7495/smeta-median-03de7495.xlsx
@@ -115,7 +115,7 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Тестовая компания · 14 октября 2026 · актуально до 13.11.2026</t>
+          <t xml:space="preserve">Тестовая компания · 14 октября 2026 · мероприятие 10.12.2026 · актуально до 13.11.2026</t>
         </is>
       </c>
     </row>
